--- a/Excels/EstadosTickets.xlsx
+++ b/Excels/EstadosTickets.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Flutter\tickets_web_app\Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\Tickets\tickets_web_app\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C2D7C21-2FCE-4F54-AFE4-DD541CB8B70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E60BE716-E9A0-4C51-899A-16673631DEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{2C0FA381-D708-4478-922F-AE5A18698AE2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{2C0FA381-D708-4478-922F-AE5A18698AE2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="3" r:id="rId1"/>
     <sheet name="Hoja2" sheetId="4" r:id="rId2"/>
+    <sheet name="Hoja3" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="47">
   <si>
     <t>Usuario</t>
   </si>
@@ -157,6 +158,27 @@
   </si>
   <si>
     <t>estado</t>
+  </si>
+  <si>
+    <t>Usuario Jefe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devuelto </t>
+  </si>
+  <si>
+    <t>Autorizar</t>
+  </si>
+  <si>
+    <t>Autorizado</t>
+  </si>
+  <si>
+    <t>Rechazado</t>
+  </si>
+  <si>
+    <t>Usuario Resolv.</t>
+  </si>
+  <si>
+    <t>Terminados</t>
   </si>
 </sst>
 </file>
@@ -312,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -342,6 +364,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -360,6 +394,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF0000FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2022,6 +2061,1962 @@
         <a:xfrm flipH="1">
           <a:off x="5836920" y="1668780"/>
           <a:ext cx="1409700" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>312420</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>434340</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>198120</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Elipse 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FF9D473-BF4B-4BF0-B6BD-B6268EC231BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2141220" y="701040"/>
+          <a:ext cx="121920" cy="137160"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-AR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>426720</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>373380</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Conector recto de flecha 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72D85D65-6B9F-48F5-BFFE-313B3AA19D32}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="99" idx="6"/>
+          <a:endCxn id="2" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1462144" y="527125"/>
+          <a:ext cx="861060" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>426720</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>213360</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Elipse 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85D81B45-C98A-4DB1-8C19-CACA0D789EB7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5791200" y="4145280"/>
+          <a:ext cx="121920" cy="137160"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-AR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>411480</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>178033</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>330275</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="Conector recto de flecha 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD0EB437-A0DA-4DB8-92DE-2394EE6927E4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="3"/>
+          <a:endCxn id="102" idx="6"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1447800" y="947653"/>
+          <a:ext cx="833195" cy="431567"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>330275</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>178033</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="Conector recto de flecha 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63D0DAEB-5F75-4642-B2C2-011D9190F875}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="3"/>
+          <a:endCxn id="7" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2159075" y="821500"/>
+          <a:ext cx="2717725" cy="3522747"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>416485</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>178033</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>345515</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>88667</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="Conector recto de flecha 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B79910C9-4501-4DB2-A4CE-1494BAD799DF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="5"/>
+          <a:endCxn id="20" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2367205" y="947653"/>
+          <a:ext cx="843430" cy="794554"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>327660</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>449580</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="Elipse 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{039AEF2D-6C78-4F2E-B452-14DECE6FF561}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3070860" y="1089660"/>
+          <a:ext cx="121920" cy="137160"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-AR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>431725</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>185653</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>365760</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="24" name="Conector recto de flecha 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CD224CD-A1A1-4BC5-9D41-4CE196783C4C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="20" idx="5"/>
+          <a:endCxn id="7" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3296845" y="1839193"/>
+          <a:ext cx="1762835" cy="2542307"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="0000FF"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>350520</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>236220</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>327660</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="29" name="Conector recto de flecha 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{072805FD-A4A1-4C2B-9065-2C2204542660}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="20" idx="2"/>
+          <a:endCxn id="102" idx="4"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="1386840" y="1447800"/>
+          <a:ext cx="1805940" cy="342900"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="0000FF"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>449580</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>388620</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="34" name="Conector recto de flecha 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8408702-25BA-4EC3-9523-0E1D0405CAB8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="20" idx="6"/>
+          <a:endCxn id="36" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3314700" y="1790700"/>
+          <a:ext cx="853440" cy="373380"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="0000FF"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>327660</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>449580</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="Elipse 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6F21189-C363-436D-81CE-BCD02189FBC3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3985260" y="1851660"/>
+          <a:ext cx="121920" cy="137160"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-AR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>439345</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>185653</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>345515</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>88667</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="37" name="Conector recto de flecha 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60EABA0C-2DA2-4B62-BCBC-BFA075D60721}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="36" idx="3"/>
+          <a:endCxn id="42" idx="7"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3182545" y="1968733"/>
+          <a:ext cx="820570" cy="284014"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent5"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>335280</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="Elipse 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEC6F146-CE7E-4D89-A058-1971684C716E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3078480" y="2232660"/>
+          <a:ext cx="121920" cy="137160"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-AR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>327660</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>449580</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>213360</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="Elipse 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{343128F4-A10E-4C42-9BD0-B3B22CA57A19}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5814060" y="2621280"/>
+          <a:ext cx="121920" cy="137160"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-AR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>388620</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>345515</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>96287</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="60" name="Conector recto de flecha 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D87769F-4816-4161-BE2E-80095F5CE351}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="36" idx="4"/>
+          <a:endCxn id="49" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4167244" y="2307964"/>
+          <a:ext cx="871295" cy="778052"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent5"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>416485</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>178033</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>358987</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>98213</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="63" name="Conector recto de flecha 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E372322D-83F2-47AE-BE1B-EC800DC30927}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="5"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2245285" y="821500"/>
+          <a:ext cx="3600102" cy="2587180"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>327660</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>449580</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="68" name="Elipse 67">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83275008-997B-4DDC-9ADE-4700D89D4C8D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5814060" y="2994660"/>
+          <a:ext cx="121920" cy="137160"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-AR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>388620</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>396240</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="69" name="Conector recto de flecha 68">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A49B93D8-04EE-4F54-A8F4-52EEF141E28A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="68" idx="4"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5875020" y="3131820"/>
+          <a:ext cx="7620" cy="274320"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>335280</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>220980</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="72" name="Elipse 71">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C670A31B-A367-411F-A03B-8046A34A0777}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5821680" y="3390900"/>
+          <a:ext cx="121920" cy="137160"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-AR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>431725</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>147553</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>327660</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="73" name="Conector recto de flecha 72">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDBCBF88-ED28-49FB-8F7D-18AFE4B5FD09}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="68" idx="2"/>
+          <a:endCxn id="90" idx="5"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="2260525" y="1235520"/>
+          <a:ext cx="3553535" cy="2212107"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>408865</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>185653</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>345515</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>96287</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="76" name="Conector recto de flecha 75">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27DD95E3-4A28-485B-867B-822834D821BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="68" idx="3"/>
+          <a:endCxn id="7" idx="7"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="4980865" y="3496120"/>
+          <a:ext cx="851050" cy="799634"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>426720</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>365760</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="82" name="Conector recto de flecha 81">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{969137F8-7EFA-417C-A5AB-ED220595D628}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="7" idx="6"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="4998720" y="3512820"/>
+          <a:ext cx="853440" cy="701040"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>350520</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>312420</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="87" name="Conector recto de flecha 86">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C386F780-212D-49A1-BCE1-EB242156F151}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="102" idx="0"/>
+          <a:endCxn id="2" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1386840" y="899160"/>
+          <a:ext cx="876300" cy="411480"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>327660</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>449580</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="90" name="Elipse 89">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D300E16C-59B5-49DA-88D9-CFAD62BAB696}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2156460" y="1051560"/>
+          <a:ext cx="121920" cy="137160"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-AR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>431725</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>50567</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>345515</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>88667</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="93" name="Conector recto de flecha 92">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECDD1232-6D75-4D98-9716-FDBD522D0BF1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="20" idx="1"/>
+          <a:endCxn id="90" idx="7"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="2382445" y="1262147"/>
+          <a:ext cx="828190" cy="480060"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="0000FF"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>426720</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="99" name="Elipse 98">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8B6FCBF-666C-4E96-968C-A9852189ABE8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="327660"/>
+          <a:ext cx="121920" cy="137160"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-AR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>289560</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>411480</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>236220</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="102" name="Elipse 101">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35ECABD1-E896-4EBF-8193-E0FF98B19848}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1203960" y="1181100"/>
+          <a:ext cx="121920" cy="137160"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-AR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="121" name="Imagen 120">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B89497FD-6D72-F2C8-5686-2EB96995E837}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1950720" y="2849880"/>
+          <a:ext cx="800100" cy="137160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>396240</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="123" name="Conector recto de flecha 122">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9FA24D07-6A1D-4D76-B7DB-7A2919012761}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="42" idx="4"/>
+          <a:endCxn id="7" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3261360" y="2743200"/>
+          <a:ext cx="1737360" cy="1706880"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="0000FF"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>327660</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="126" name="Conector recto de flecha 125">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26BBCE5A-CEC0-4634-BA6A-8D126D889919}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="42" idx="6"/>
+          <a:endCxn id="49" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3322320" y="2674620"/>
+          <a:ext cx="1699260" cy="449580"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="0000FF"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>440690</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>160385</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>327660</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="129" name="Conector recto de flecha 128">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1847C3C1-726D-45DC-A0B3-96FE47195DB1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="49" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3304914" y="1818856"/>
+          <a:ext cx="1715770" cy="1315653"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="0000FF"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>345515</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>147553</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>353135</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>200893</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="132" name="Conector recto de flecha 131">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDDE6142-8266-42D6-90FE-7CC3EE553342}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="72" idx="3"/>
+          <a:endCxn id="90" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="2295339" y="1362271"/>
+          <a:ext cx="3665220" cy="2715857"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2381,14 +4376,14 @@
       </c>
     </row>
     <row r="3" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="19"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="3:9" x14ac:dyDescent="0.2">
       <c r="D4" s="7" t="s">
@@ -2608,13 +4603,13 @@
       </c>
     </row>
     <row r="28" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
     </row>
     <row r="29" spans="3:9" x14ac:dyDescent="0.2">
       <c r="D29" s="7" t="s">
@@ -3011,4 +5006,115 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E58178F-AE6D-4D45-9087-AA6F2CA87697}">
+  <dimension ref="B2:N22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="1.77734375" style="17" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" style="17"/>
+    <col min="3" max="3" width="1.77734375" style="17" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="17"/>
+    <col min="5" max="5" width="1.77734375" style="17" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" style="17"/>
+    <col min="7" max="7" width="1.77734375" style="17" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" style="17"/>
+    <col min="9" max="9" width="1.77734375" style="17" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" style="17"/>
+    <col min="11" max="11" width="1.77734375" style="17" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" style="17"/>
+    <col min="13" max="13" width="1.77734375" style="17" customWidth="1"/>
+    <col min="14" max="16384" width="11.5546875" style="17"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="D2" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="20"/>
+      <c r="F2" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="20"/>
+      <c r="H2" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" s="20"/>
+      <c r="J2" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" s="20"/>
+      <c r="L2" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="M2" s="20"/>
+      <c r="N2" s="19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="18"/>
+    </row>
+    <row r="6" spans="2:14" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="18"/>
+    </row>
+    <row r="8" spans="2:14" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="18"/>
+      <c r="F8" s="18"/>
+    </row>
+    <row r="10" spans="2:14" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="18"/>
+    </row>
+    <row r="12" spans="2:14" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="J12" s="18"/>
+    </row>
+    <row r="14" spans="2:14" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="18"/>
+    </row>
+    <row r="16" spans="2:14" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="L16" s="18"/>
+    </row>
+    <row r="18" spans="2:14" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="N18" s="18"/>
+    </row>
+    <row r="20" spans="2:14" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="N20" s="18"/>
+    </row>
+    <row r="22" spans="2:14" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="L22" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>